--- a/classifier/dataset/dtts.xlsx
+++ b/classifier/dataset/dtts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kuliah\Akademik\Matkul\Semester 4\Kecerdasan Komputasional\knn_classifier\classifier\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDE78FA-5908-4879-B4CD-4BFD4086113A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DA80588-637F-4752-B6C3-0D7FAF2ED911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -136,7 +136,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,8 +158,14 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -175,6 +181,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF8FAFC"/>
         <bgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E3A8A"/>
+        <bgColor rgb="FF1E3A8A"/>
       </patternFill>
     </fill>
   </fills>
@@ -205,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -222,6 +234,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -528,53 +543,53 @@
   <dimension ref="A1:Q1900"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="7" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
